--- a/data/trans_orig/IP07KS_C10_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07KS_C10_2023-Habitat-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de poder prestar atención en 2023 (tasa de respuesta: 99,83%)</t>
+          <t>Menores según la frecuencia de poder prestar atención, percibida por el/la menor en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>14528</t>
+          <t>25813</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10431</t>
+          <t>18776</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19475</t>
+          <t>37128</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>27069</t>
+          <t>16074</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18192</t>
+          <t>11648</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38493</t>
+          <t>21689</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>41596</t>
+          <t>41887</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31680</t>
+          <t>32990</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55303</t>
+          <t>55374</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>67,77%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16178</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7714</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22633</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>34,04%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>16,23%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>47,62%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>15464</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>10763</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>19727</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>49,61%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>34,53%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>63,28%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15462</t>
+          <t>16809</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7469</t>
+          <t>11779</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23408</t>
+          <t>21432</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>30926</t>
+          <t>32987</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19289</t>
+          <t>20556</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40527</t>
+          <t>41827</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,19%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4633</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1634</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9941</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>9,75%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>20,92%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1181</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4206</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1296</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>3,79%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>13,49%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>4615</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1459</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>9427</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>9,61%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>3,04%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>5796</t>
+          <t>5929</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2548</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10964</t>
+          <t>10940</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -1059,107 +1059,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>904</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4615</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,71%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>876</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5564</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>904</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4275</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>11,59%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>876</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>5119</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>47528</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>47528</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>47528</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>79194</t>
+          <t>81708</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>79194</t>
+          <t>81708</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>79194</t>
+          <t>81708</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>47957</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>37198</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>58368</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>47,47%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>36,82%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>57,77%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>25589</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>19835</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>32038</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>47,71%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>36,98%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>59,74%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>48051</t>
+          <t>27425</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37703</t>
+          <t>21126</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58293</t>
+          <t>33960</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>73640</t>
+          <t>75382</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61019</t>
+          <t>63942</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86206</t>
+          <t>87765</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,46%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>43059</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>32952</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>53828</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>42,62%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>32,62%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>53,28%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>25517</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>19762</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>31959</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>47,58%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>36,85%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>59,59%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>43218</t>
+          <t>27164</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33701</t>
+          <t>21075</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53899</t>
+          <t>34217</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>68734</t>
+          <t>70223</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>57253</t>
+          <t>58495</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>82366</t>
+          <t>82066</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>51,86%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7783</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3387</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>16358</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>16,19%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1373</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4431</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1408</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5249</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,26%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>8276</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>3626</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>14992</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>8,12%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>9649</t>
+          <t>9191</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>4752</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18074</t>
+          <t>16479</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>7620</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1774</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8174</t>
+          <t>6748</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10425</t>
+          <t>10135</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -1854,107 +1854,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>574</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2984</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,95%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3609</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>2953</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2955</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>101027</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>101027</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>101027</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>53633</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>53633</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>53633</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>101915</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>101915</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>101915</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>155548</t>
+          <t>158252</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>155548</t>
+          <t>158252</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>155548</t>
+          <t>158252</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>37868</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>28082</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>46002</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>58,41%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>43,32%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>70,96%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>26684</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>8864</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>46046</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>36,97%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>12,28%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>63,79%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>38577</t>
+          <t>26968</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28810</t>
+          <t>19767</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47474</t>
+          <t>32963</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>65260</t>
+          <t>64836</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34427</t>
+          <t>52984</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>85753</t>
+          <t>76489</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>67,01%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>23263</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>15631</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>33602</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>35,88%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>24,11%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>51,83%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>43565</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>22924</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>62226</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>60,35%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>31,76%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>86,21%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22866</t>
+          <t>20325</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14677</t>
+          <t>14261</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33473</t>
+          <t>27837</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>66431</t>
+          <t>43588</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>44856</t>
+          <t>32592</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>98823</t>
+          <t>56158</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>49,2%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3698</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>928</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>9389</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>5,7%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>14,48%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>1935</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>6121</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>8,48%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3535</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>343</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8584</t>
+          <t>5894</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>5470</t>
+          <t>5724</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11036</t>
+          <t>10966</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>64829</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>64829</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>64829</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>72183</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>72183</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>72183</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>64978</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>64978</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>64978</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>137161</t>
+          <t>114147</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137161</t>
+          <t>114147</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137161</t>
+          <t>114147</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>27045</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>20232</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>33524</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>48,45%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>36,24%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>60,06%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>30492</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>24418</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>36816</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>57,01%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>45,66%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>68,84%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>27240</t>
+          <t>31755</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20555</t>
+          <t>25675</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34138</t>
+          <t>38982</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>57732</t>
+          <t>58800</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>48542</t>
+          <t>49174</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67594</t>
+          <t>68664</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>60,93%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>20829</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>15296</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>27582</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>37,31%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>27,4%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>49,41%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>20660</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>14424</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>26544</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>38,63%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>26,97%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>49,63%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>21068</t>
+          <t>22659</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>14654</t>
+          <t>15890</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>28267</t>
+          <t>28901</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>41728</t>
+          <t>43488</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>33025</t>
+          <t>34963</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>50586</t>
+          <t>53973</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>47,9%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>7009</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>3269</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>13254</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>12,56%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>5,86%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>23,74%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>2331</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>5448</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>10,19%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7158</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3354</t>
+          <t>612</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14039</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>9489</t>
+          <t>9460</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>4743</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>15895</t>
+          <t>15978</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -3105,107 +3105,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>938</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>4307</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>7,72%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>905</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>4507</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>8,0%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>905</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>4496</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>55820</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>55820</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>55820</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>53483</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>53483</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>53483</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>56371</t>
+          <t>56865</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>56371</t>
+          <t>56865</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>56371</t>
+          <t>56865</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>109854</t>
+          <t>112685</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>109854</t>
+          <t>112685</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>109854</t>
+          <t>112685</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,72 +3448,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>138682</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>120430</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>157011</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>51,52%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>44,74%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>58,32%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>97293</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>61452</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>117701</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>46,23%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>29,2%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>55,92%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>140937</t>
+          <t>102223</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>121030</t>
+          <t>89629</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>161428</t>
+          <t>115935</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>238229</t>
+          <t>240905</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>196708</t>
+          <t>219774</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>264467</t>
+          <t>264584</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>56,68%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>103328</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>85591</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>121521</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>38,38%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>31,79%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>45,14%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>105205</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>84149</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>144460</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>49,99%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>39,98%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>68,64%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>102614</t>
+          <t>86957</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>83874</t>
+          <t>74334</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>121684</t>
+          <t>99397</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>207819</t>
+          <t>190285</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>182097</t>
+          <t>167962</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>256062</t>
+          <t>212585</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>45,54%</t>
         </is>
       </c>
     </row>
@@ -3674,72 +3674,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>23123</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>15647</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>34059</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>8,59%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>5,81%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>12,65%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>6820</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>3287</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>12548</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>23583</t>
+          <t>7181</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>15416</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>34377</t>
+          <t>12519</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>30403</t>
+          <t>30304</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>21512</t>
+          <t>21553</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>41381</t>
+          <t>41263</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -3787,72 +3787,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>3496</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>11730</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>4,36%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>1154</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>6629</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>1227</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>6241</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>3,15%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>3555</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>864</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>11452</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>11747</t>
+          <t>12498</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -3900,107 +3900,107 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>574</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>3233</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="P32" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>3253</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>2976</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>3253</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>269203</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>269203</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>269203</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>271285</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>271285</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>271285</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>481757</t>
+          <t>466791</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>481757</t>
+          <t>466791</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>481757</t>
+          <t>466791</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
